--- a/data/trans_dic/IP07_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP07_R2-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,8%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,57; 5,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,29</t>
+          <t>1,73; 7,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,22</t>
+          <t>1,54; 7,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>2,95; 14,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,98</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,31</t>
+          <t>1,42; 6,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,69</t>
+          <t>0,44; 4,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 14,64</t>
+          <t>0,0; 9,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,41</t>
+          <t>0,59; 3,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,37</t>
+          <t>2,01; 5,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,73</t>
+          <t>1,42; 4,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,59</t>
+          <t>2,37; 9,49</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,06%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,32%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,28</t>
+          <t>1,91; 5,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,93</t>
+          <t>0,24; 2,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,89</t>
+          <t>0,25; 2,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,3</t>
+          <t>0,63; 4,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,17</t>
+          <t>0,25; 2,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,02</t>
+          <t>0,94; 4,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,2</t>
+          <t>0,88; 4,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,12</t>
+          <t>0,6; 5,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,27</t>
+          <t>1,3; 3,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,35</t>
+          <t>0,68; 2,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,79</t>
+          <t>0,83; 2,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,43</t>
+          <t>0,81; 3,59</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,12%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,32</t>
+          <t>3,14; 9,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,01</t>
+          <t>1,41; 5,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,55</t>
+          <t>1,03; 5,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,56</t>
+          <t>1,05; 6,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,6</t>
+          <t>0,58; 4,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,12</t>
+          <t>0,84; 5,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,1</t>
+          <t>0,34; 3,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,54</t>
+          <t>1,72; 6,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,21</t>
+          <t>2,41; 6,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,48</t>
+          <t>1,48; 4,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,35</t>
+          <t>0,98; 3,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,85</t>
+          <t>1,69; 4,88</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,75</t>
+          <t>1,32; 5,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,14</t>
+          <t>1,84; 7,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,41</t>
+          <t>0,75; 4,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,37</t>
+          <t>0,76; 3,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,23</t>
+          <t>1,65; 5,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,47</t>
+          <t>0,76; 4,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,64</t>
+          <t>0,73; 4,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,62</t>
+          <t>1,07; 4,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,66</t>
+          <t>1,81; 4,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,74</t>
+          <t>1,72; 4,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,75</t>
+          <t>1,09; 3,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,54</t>
+          <t>1,25; 3,56</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,74</t>
+          <t>2,57; 4,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,42</t>
+          <t>1,67; 3,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,05</t>
+          <t>1,29; 3,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,63</t>
+          <t>1,54; 3,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,7</t>
+          <t>1,01; 2,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,51</t>
+          <t>1,53; 3,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,08</t>
+          <t>1,21; 2,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,62</t>
+          <t>1,58; 3,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,35</t>
+          <t>2,04; 3,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,21</t>
+          <t>1,85; 3,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,66</t>
+          <t>1,49; 2,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,36</t>
+          <t>1,85; 3,3</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5118</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4542</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3757</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1070</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4755</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2362</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2664</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5118</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4542</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5062</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4033</t>
+          <t>697; 6698</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2044; 9235</t>
+          <t>2512; 10282</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>583; 5529</t>
+          <t>1906; 8904</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4929</t>
+          <t>1489; 7544</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>661; 6040</t>
+          <t>0; 3682</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2294; 9173</t>
+          <t>2084; 9967</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1993; 9484</t>
+          <t>575; 5851</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1426; 8996</t>
+          <t>0; 4761</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1338; 7769</t>
+          <t>1334; 8023</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5889; 15690</t>
+          <t>5860; 15530</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3714; 12019</t>
+          <t>3623; 11709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2677; 11402</t>
+          <t>2433; 9743</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8801</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2540</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2815</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1970</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4826</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4833</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2745</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8801</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2540</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5364</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>614; 5776</t>
+          <t>4819; 14706</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1961; 9228</t>
+          <t>650; 5449</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1806; 10185</t>
+          <t>655; 6675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634; 6847</t>
+          <t>992; 7125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4787; 15554</t>
+          <t>621; 5209</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>646; 5381</t>
+          <t>2203; 9971</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>630; 5660</t>
+          <t>1836; 9864</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>974; 7514</t>
+          <t>878; 7567</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6624; 16533</t>
+          <t>6576; 16783</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3307; 11761</t>
+          <t>3382; 12135</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3896; 12987</t>
+          <t>3871; 12590</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2825; 11742</t>
+          <t>2443; 10878</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7924</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4887</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4601</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5208</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2700</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3513</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2747</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7924</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4601</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11207</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>684; 6788</t>
+          <t>4440; 13435</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1315; 7861</t>
+          <t>2229; 9250</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>972; 6682</t>
+          <t>1936; 10345</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2731; 11413</t>
+          <t>2097; 12007</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4356; 13580</t>
+          <t>734; 6075</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2075; 9707</t>
+          <t>1327; 8199</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2095; 9612</t>
+          <t>645; 6730</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2277; 11770</t>
+          <t>3025; 11852</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6163; 16717</t>
+          <t>6488; 16730</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4299; 14140</t>
+          <t>4683; 13831</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3891; 12640</t>
+          <t>3689; 12495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6216; 18757</t>
+          <t>6359; 18321</t>
         </is>
       </c>
     </row>
@@ -2138,37 +2138,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6724</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5905</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3526</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3456</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11076</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6024</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6724</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3816</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>11638</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2716; 11156</t>
+          <t>2695; 10759</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1339; 8776</t>
+          <t>3312; 12744</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1196; 7615</t>
+          <t>1293; 8399</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4061; 34087</t>
+          <t>2211; 10891</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3269; 10713</t>
+          <t>3211; 10878</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3397; 11647</t>
+          <t>1299; 7819</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1336; 8016</t>
+          <t>1264; 7522</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2195; 11049</t>
+          <t>2758; 11955</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7309; 18575</t>
+          <t>7234; 19056</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5944; 16609</t>
+          <t>6034; 17253</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3619; 12961</t>
+          <t>3763; 13644</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8523; 37989</t>
+          <t>6889; 19538</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25414</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18726</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>17131</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>11645</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>16619</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>13398</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>21144</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25414</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18726</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15499</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>33271</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7265; 18649</t>
+          <t>18490; 35297</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10563; 24280</t>
+          <t>12486; 26716</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8737; 21336</t>
+          <t>9584; 23187</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12880; 44185</t>
+          <t>10764; 25332</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18030; 33821</t>
+          <t>6868; 18628</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13095; 26308</t>
+          <t>10857; 24748</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9417; 22821</t>
+          <t>8496; 20805</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11965; 27555</t>
+          <t>9944; 24126</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27533; 46954</t>
+          <t>28607; 47605</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26198; 46783</t>
+          <t>27038; 46163</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20921; 38333</t>
+          <t>21541; 37817</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28069; 62247</t>
+          <t>24678; 43909</t>
         </is>
       </c>
     </row>
